--- a/stage-5/52_pilot_scorecard.xlsx
+++ b/stage-5/52_pilot_scorecard.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case replay" sheetId="1" r:id="Refc40dd8eb7d4d32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilot scorecard" sheetId="2" r:id="Rbfefd4181aa64400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision log" sheetId="3" r:id="R58ea74f7e3144351"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case replay" sheetId="1" r:id="R6fee337afbc34e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilot scorecard" sheetId="2" r:id="Rd6bfe769f8214081"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision log" sheetId="3" r:id="R9041cbf58bcd44df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -212,7 +212,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="150">
+  <x:cellXfs count="146">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -411,19 +411,13 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -541,9 +535,6 @@
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="203" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
@@ -570,9 +561,6 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -810,610 +798,610 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="96" t="str">
+      <x:c r="A1" s="94" t="str">
         <x:v>case_id</x:v>
       </x:c>
-      <x:c r="B1" s="96" t="str">
+      <x:c r="B1" s="94" t="str">
         <x:v>arm</x:v>
       </x:c>
-      <x:c r="C1" s="96" t="str">
+      <x:c r="C1" s="94" t="str">
         <x:v>region</x:v>
       </x:c>
-      <x:c r="D1" s="96" t="str">
+      <x:c r="D1" s="94" t="str">
         <x:v>prime</x:v>
       </x:c>
-      <x:c r="E1" s="96" t="str">
+      <x:c r="E1" s="94" t="str">
         <x:v>order_value_inr</x:v>
       </x:c>
-      <x:c r="F1" s="96" t="str">
+      <x:c r="F1" s="94" t="str">
         <x:v>event_conflict</x:v>
       </x:c>
-      <x:c r="G1" s="96" t="str">
+      <x:c r="G1" s="94" t="str">
         <x:v>recovery_option</x:v>
       </x:c>
-      <x:c r="H1" s="96" t="str">
+      <x:c r="H1" s="94" t="str">
         <x:v>eligible</x:v>
       </x:c>
-      <x:c r="I1" s="96" t="str">
+      <x:c r="I1" s="94" t="str">
         <x:v>repeat_contacts</x:v>
       </x:c>
-      <x:c r="J1" s="96" t="str">
+      <x:c r="J1" s="94" t="str">
         <x:v>resolution_hours</x:v>
       </x:c>
-      <x:c r="K1" s="96" t="str">
+      <x:c r="K1" s="94" t="str">
         <x:v>understood_next</x:v>
       </x:c>
-      <x:c r="L1" s="96" t="str">
+      <x:c r="L1" s="94" t="str">
         <x:v>incorrect_recovery</x:v>
       </x:c>
-      <x:c r="M1" s="96" t="str">
+      <x:c r="M1" s="94" t="str">
         <x:v>sla_breach</x:v>
       </x:c>
-      <x:c r="N1" s="96" t="str">
+      <x:c r="N1" s="94" t="str">
         <x:v>support_contacts</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="97" t="str">
+      <x:c r="A2" s="95" t="str">
         <x:v>SYN-001</x:v>
       </x:c>
-      <x:c r="B2" s="97" t="str">
+      <x:c r="B2" s="95" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C2" s="97" t="str">
+      <x:c r="C2" s="95" t="str">
         <x:v>North</x:v>
       </x:c>
-      <x:c r="D2" s="97" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E2" s="98" t="str">
+      <x:c r="D2" s="95" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E2" s="96" t="str">
         <x:v>2499</x:v>
       </x:c>
-      <x:c r="F2" s="97" t="str">
+      <x:c r="F2" s="95" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G2" s="97" t="str">
+      <x:c r="G2" s="95" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H2" s="97" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I2" s="99" t="str">
+      <x:c r="H2" s="95" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I2" s="97" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J2" s="99" t="str">
+      <x:c r="J2" s="97" t="str">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K2" s="100" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L2" s="100" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="100" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N2" s="99" t="str">
+      <x:c r="K2" s="98" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L2" s="98" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="98" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N2" s="97" t="str">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="101" t="str">
+      <x:c r="A3" s="99" t="str">
         <x:v>SYN-002</x:v>
       </x:c>
-      <x:c r="B3" s="101" t="str">
+      <x:c r="B3" s="99" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C3" s="101" t="str">
+      <x:c r="C3" s="99" t="str">
         <x:v>North</x:v>
       </x:c>
-      <x:c r="D3" s="101" t="str">
+      <x:c r="D3" s="99" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="E3" s="102" t="str">
+      <x:c r="E3" s="100" t="str">
         <x:v>899</x:v>
       </x:c>
-      <x:c r="F3" s="101" t="str">
+      <x:c r="F3" s="99" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G3" s="101" t="str">
+      <x:c r="G3" s="99" t="str">
         <x:v>REPLACEMENT</x:v>
       </x:c>
-      <x:c r="H3" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I3" s="103" t="str">
+      <x:c r="H3" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I3" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J3" s="103" t="str">
+      <x:c r="J3" s="101" t="str">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="K3" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L3" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M3" s="104" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N3" s="103" t="str">
+      <x:c r="K3" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L3" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" s="102" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N3" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="101" t="str">
+      <x:c r="A4" s="99" t="str">
         <x:v>SYN-003</x:v>
       </x:c>
-      <x:c r="B4" s="101" t="str">
+      <x:c r="B4" s="99" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C4" s="101" t="str">
+      <x:c r="C4" s="99" t="str">
         <x:v>West</x:v>
       </x:c>
-      <x:c r="D4" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E4" s="102" t="str">
+      <x:c r="D4" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E4" s="100" t="str">
         <x:v>4999</x:v>
       </x:c>
-      <x:c r="F4" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G4" s="101" t="str">
+      <x:c r="F4" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G4" s="99" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H4" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I4" s="103" t="str">
+      <x:c r="H4" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I4" s="101" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J4" s="103" t="str">
+      <x:c r="J4" s="101" t="str">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="K4" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L4" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M4" s="104" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N4" s="103" t="str">
+      <x:c r="K4" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L4" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="102" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N4" s="101" t="str">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="101" t="str">
+      <x:c r="A5" s="99" t="str">
         <x:v>SYN-004</x:v>
       </x:c>
-      <x:c r="B5" s="101" t="str">
+      <x:c r="B5" s="99" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C5" s="101" t="str">
+      <x:c r="C5" s="99" t="str">
         <x:v>South</x:v>
       </x:c>
-      <x:c r="D5" s="101" t="str">
+      <x:c r="D5" s="99" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="E5" s="102" t="str">
+      <x:c r="E5" s="100" t="str">
         <x:v>1799</x:v>
       </x:c>
-      <x:c r="F5" s="101" t="str">
+      <x:c r="F5" s="99" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G5" s="101" t="str">
+      <x:c r="G5" s="99" t="str">
         <x:v>DELIVERY_RETRY</x:v>
       </x:c>
-      <x:c r="H5" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I5" s="103" t="str">
+      <x:c r="H5" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I5" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J5" s="103" t="str">
+      <x:c r="J5" s="101" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K5" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L5" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M5" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="103" t="str">
+      <x:c r="K5" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="101" t="str">
+      <x:c r="A6" s="99" t="str">
         <x:v>SYN-005</x:v>
       </x:c>
-      <x:c r="B6" s="101" t="str">
+      <x:c r="B6" s="99" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C6" s="101" t="str">
+      <x:c r="C6" s="99" t="str">
         <x:v>East</x:v>
       </x:c>
-      <x:c r="D6" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E6" s="102" t="str">
+      <x:c r="D6" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E6" s="100" t="str">
         <x:v>3299</x:v>
       </x:c>
-      <x:c r="F6" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G6" s="101" t="str">
+      <x:c r="F6" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G6" s="99" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H6" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I6" s="103" t="str">
+      <x:c r="H6" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I6" s="101" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J6" s="103" t="str">
+      <x:c r="J6" s="101" t="str">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K6" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L6" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="104" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N6" s="103" t="str">
+      <x:c r="K6" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="102" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="101" t="str">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="101" t="str">
+      <x:c r="A7" s="99" t="str">
         <x:v>SYN-006</x:v>
       </x:c>
-      <x:c r="B7" s="101" t="str">
+      <x:c r="B7" s="99" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C7" s="101" t="str">
+      <x:c r="C7" s="99" t="str">
         <x:v>North</x:v>
       </x:c>
-      <x:c r="D7" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E7" s="102" t="str">
+      <x:c r="D7" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E7" s="100" t="str">
         <x:v>1299</x:v>
       </x:c>
-      <x:c r="F7" s="101" t="str">
+      <x:c r="F7" s="99" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G7" s="101" t="str">
+      <x:c r="G7" s="99" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H7" s="101" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I7" s="103" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J7" s="103" t="str">
+      <x:c r="H7" s="99" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I7" s="101" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="101" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K7" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7" s="104" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="103" t="str">
+      <x:c r="K7" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="102" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="101" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="105" t="str">
+      <x:c r="A8" s="103" t="str">
         <x:v>SYN-007</x:v>
       </x:c>
-      <x:c r="B8" s="105" t="str">
+      <x:c r="B8" s="103" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="C8" s="105" t="str">
+      <x:c r="C8" s="103" t="str">
         <x:v>North</x:v>
       </x:c>
-      <x:c r="D8" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E8" s="106" t="str">
+      <x:c r="D8" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E8" s="104" t="str">
         <x:v>2499</x:v>
       </x:c>
-      <x:c r="F8" s="105" t="str">
+      <x:c r="F8" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G8" s="105" t="str">
+      <x:c r="G8" s="103" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H8" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I8" s="107" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J8" s="107" t="str">
+      <x:c r="H8" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I8" s="105" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="105" t="str">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K8" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L8" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M8" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="107" t="str">
+      <x:c r="K8" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L8" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="105" t="str">
+      <x:c r="A9" s="103" t="str">
         <x:v>SYN-008</x:v>
       </x:c>
-      <x:c r="B9" s="105" t="str">
+      <x:c r="B9" s="103" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="C9" s="105" t="str">
+      <x:c r="C9" s="103" t="str">
         <x:v>North</x:v>
       </x:c>
-      <x:c r="D9" s="105" t="str">
+      <x:c r="D9" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="E9" s="106" t="str">
+      <x:c r="E9" s="104" t="str">
         <x:v>899</x:v>
       </x:c>
-      <x:c r="F9" s="105" t="str">
+      <x:c r="F9" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G9" s="105" t="str">
+      <x:c r="G9" s="103" t="str">
         <x:v>REPLACEMENT</x:v>
       </x:c>
-      <x:c r="H9" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I9" s="107" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J9" s="107" t="str">
+      <x:c r="H9" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I9" s="105" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="105" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K9" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L9" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="107" t="str">
+      <x:c r="K9" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L9" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="105" t="str">
+      <x:c r="A10" s="103" t="str">
         <x:v>SYN-009</x:v>
       </x:c>
-      <x:c r="B10" s="105" t="str">
+      <x:c r="B10" s="103" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="C10" s="105" t="str">
+      <x:c r="C10" s="103" t="str">
         <x:v>West</x:v>
       </x:c>
-      <x:c r="D10" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E10" s="106" t="str">
+      <x:c r="D10" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E10" s="104" t="str">
         <x:v>4999</x:v>
       </x:c>
-      <x:c r="F10" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G10" s="105" t="str">
+      <x:c r="F10" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G10" s="103" t="str">
         <x:v>SUPPORT_ESCALATION</x:v>
       </x:c>
-      <x:c r="H10" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I10" s="107" t="str">
+      <x:c r="H10" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I10" s="105" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J10" s="107" t="str">
+      <x:c r="J10" s="105" t="str">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K10" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L10" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N10" s="107" t="str">
+      <x:c r="K10" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L10" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N10" s="105" t="str">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="105" t="str">
+      <x:c r="A11" s="103" t="str">
         <x:v>SYN-010</x:v>
       </x:c>
-      <x:c r="B11" s="105" t="str">
+      <x:c r="B11" s="103" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="C11" s="105" t="str">
+      <x:c r="C11" s="103" t="str">
         <x:v>South</x:v>
       </x:c>
-      <x:c r="D11" s="105" t="str">
+      <x:c r="D11" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="E11" s="106" t="str">
+      <x:c r="E11" s="104" t="str">
         <x:v>1799</x:v>
       </x:c>
-      <x:c r="F11" s="105" t="str">
+      <x:c r="F11" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G11" s="105" t="str">
+      <x:c r="G11" s="103" t="str">
         <x:v>DELIVERY_RETRY</x:v>
       </x:c>
-      <x:c r="H11" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I11" s="107" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="107" t="str">
+      <x:c r="H11" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I11" s="105" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="105" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K11" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L11" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="107" t="str">
+      <x:c r="K11" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L11" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="105" t="str">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="105" t="str">
+      <x:c r="A12" s="103" t="str">
         <x:v>SYN-011</x:v>
       </x:c>
-      <x:c r="B12" s="105" t="str">
+      <x:c r="B12" s="103" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="C12" s="105" t="str">
+      <x:c r="C12" s="103" t="str">
         <x:v>East</x:v>
       </x:c>
-      <x:c r="D12" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E12" s="106" t="str">
+      <x:c r="D12" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E12" s="104" t="str">
         <x:v>3299</x:v>
       </x:c>
-      <x:c r="F12" s="105" t="str">
+      <x:c r="F12" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G12" s="105" t="str">
+      <x:c r="G12" s="103" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H12" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I12" s="107" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J12" s="107" t="str">
+      <x:c r="H12" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I12" s="105" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="105" t="str">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K12" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L12" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="107" t="str">
+      <x:c r="K12" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="105" t="str">
+      <x:c r="A13" s="103" t="str">
         <x:v>SYN-012</x:v>
       </x:c>
-      <x:c r="B13" s="105" t="str">
+      <x:c r="B13" s="103" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="C13" s="105" t="str">
+      <x:c r="C13" s="103" t="str">
         <x:v>North</x:v>
       </x:c>
-      <x:c r="D13" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E13" s="106" t="str">
+      <x:c r="D13" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E13" s="104" t="str">
         <x:v>1299</x:v>
       </x:c>
-      <x:c r="F13" s="105" t="str">
+      <x:c r="F13" s="103" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="G13" s="105" t="str">
+      <x:c r="G13" s="103" t="str">
         <x:v>REFUND</x:v>
       </x:c>
-      <x:c r="H13" s="105" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I13" s="107" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="107" t="str">
+      <x:c r="H13" s="103" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I13" s="105" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="105" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K13" s="108" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L13" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="108" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="107" t="str">
+      <x:c r="K13" s="106" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L13" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="106" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="105" t="str">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="109"/>
-      <x:c r="B14" s="109"/>
-      <x:c r="C14" s="109"/>
-      <x:c r="D14" s="109"/>
-      <x:c r="E14" s="109"/>
-      <x:c r="F14" s="109"/>
-      <x:c r="G14" s="109"/>
-      <x:c r="H14" s="109"/>
-      <x:c r="I14" s="109"/>
-      <x:c r="J14" s="109"/>
-      <x:c r="K14" s="109"/>
-      <x:c r="L14" s="109"/>
-      <x:c r="M14" s="109"/>
-      <x:c r="N14" s="109"/>
+      <x:c r="A14" s="107"/>
+      <x:c r="B14" s="107"/>
+      <x:c r="C14" s="107"/>
+      <x:c r="D14" s="107"/>
+      <x:c r="E14" s="107"/>
+      <x:c r="F14" s="107"/>
+      <x:c r="G14" s="107"/>
+      <x:c r="H14" s="107"/>
+      <x:c r="I14" s="107"/>
+      <x:c r="J14" s="107"/>
+      <x:c r="K14" s="107"/>
+      <x:c r="L14" s="107"/>
+      <x:c r="M14" s="107"/>
+      <x:c r="N14" s="107"/>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
-      <x:c r="A15" s="110" t="str">
-        <x:v>Synthetic worksample data only: demonstrates the scorecard calculation path; not Amazon internal telemetry or live pilot evidence.</x:v>
-      </x:c>
-      <x:c r="B15" s="110"/>
-      <x:c r="C15" s="110"/>
-      <x:c r="D15" s="110"/>
-      <x:c r="E15" s="110"/>
-      <x:c r="F15" s="110"/>
-      <x:c r="G15" s="110"/>
-      <x:c r="H15" s="110"/>
-      <x:c r="I15" s="110"/>
-      <x:c r="J15" s="110"/>
-      <x:c r="K15" s="110"/>
-      <x:c r="L15" s="110"/>
-      <x:c r="M15" s="110"/>
-      <x:c r="N15" s="110"/>
+      <x:c r="A15" s="108" t="str">
+        <x:v>Synthetic worksample data only: confirmed resolution within SLA is derived as 1 − SLA breach for mechanics; not Amazon internal telemetry or live pilot evidence.</x:v>
+      </x:c>
+      <x:c r="B15" s="108"/>
+      <x:c r="C15" s="108"/>
+      <x:c r="D15" s="108"/>
+      <x:c r="E15" s="108"/>
+      <x:c r="F15" s="108"/>
+      <x:c r="G15" s="108"/>
+      <x:c r="H15" s="108"/>
+      <x:c r="I15" s="108"/>
+      <x:c r="J15" s="108"/>
+      <x:c r="K15" s="108"/>
+      <x:c r="L15" s="108"/>
+      <x:c r="M15" s="108"/>
+      <x:c r="N15" s="108"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1438,279 +1426,299 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="124" t="str">
         <x:v>Stage 5 — Pilot Scorecard</x:v>
       </x:c>
-      <x:c r="B1" s="109"/>
-      <x:c r="C1" s="109"/>
-      <x:c r="D1" s="109"/>
-      <x:c r="E1" s="109"/>
-      <x:c r="F1" s="109"/>
-      <x:c r="G1" s="109"/>
-      <x:c r="H1" s="109"/>
+      <x:c r="B1" s="107"/>
+      <x:c r="C1" s="107"/>
+      <x:c r="D1" s="107"/>
+      <x:c r="E1" s="107"/>
+      <x:c r="F1" s="107"/>
+      <x:c r="G1" s="107"/>
+      <x:c r="H1" s="107"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="127" t="str">
+      <x:c r="A2" s="125" t="str">
         <x:v>Synthetic replay | Baseline versus proposed experience | Do not treat as production evidence</x:v>
       </x:c>
-      <x:c r="B2" s="109"/>
-      <x:c r="C2" s="109"/>
-      <x:c r="D2" s="109"/>
-      <x:c r="E2" s="109"/>
-      <x:c r="F2" s="109"/>
-      <x:c r="G2" s="109"/>
-      <x:c r="H2" s="109"/>
+      <x:c r="B2" s="107"/>
+      <x:c r="C2" s="107"/>
+      <x:c r="D2" s="107"/>
+      <x:c r="E2" s="107"/>
+      <x:c r="F2" s="107"/>
+      <x:c r="G2" s="107"/>
+      <x:c r="H2" s="107"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="109"/>
-      <x:c r="B3" s="109"/>
-      <x:c r="C3" s="109"/>
-      <x:c r="D3" s="109"/>
-      <x:c r="E3" s="109"/>
-      <x:c r="F3" s="109"/>
-      <x:c r="G3" s="109"/>
-      <x:c r="H3" s="109"/>
+      <x:c r="A3" s="107"/>
+      <x:c r="B3" s="107"/>
+      <x:c r="C3" s="107"/>
+      <x:c r="D3" s="107"/>
+      <x:c r="E3" s="107"/>
+      <x:c r="F3" s="107"/>
+      <x:c r="G3" s="107"/>
+      <x:c r="H3" s="107"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="128" t="str">
+      <x:c r="A4" s="126" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B4" s="129" t="str">
+      <x:c r="B4" s="127" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="C4" s="129" t="str">
+      <x:c r="C4" s="127" t="str">
         <x:v>Proposed</x:v>
       </x:c>
-      <x:c r="D4" s="129" t="str">
+      <x:c r="D4" s="127" t="str">
         <x:v>Change</x:v>
       </x:c>
-      <x:c r="E4" s="129" t="str">
+      <x:c r="E4" s="127" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="F4" s="129" t="str">
+      <x:c r="F4" s="127" t="str">
         <x:v>Check</x:v>
       </x:c>
-      <x:c r="G4" s="129" t="str">
+      <x:c r="G4" s="127" t="str">
         <x:v>Definition</x:v>
       </x:c>
-      <x:c r="H4" s="130" t="str">
+      <x:c r="H4" s="128" t="str">
         <x:v>Evidence status</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
-      <x:c r="A5" s="131" t="str">
+      <x:c r="A5" s="129" t="str">
+        <x:v>Confirmed resolution within promised SLA</x:v>
+      </x:c>
+      <x:c r="B5" s="130" t="n">
+        <x:f>1-SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$M$2:$M$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
+        <x:v>0.33333333333333337</x:v>
+      </x:c>
+      <x:c r="C5" s="130" t="n">
+        <x:f>1-SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$M$2:$M$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
+      <x:c r="D5" s="130" t="n">
+        <x:f>C5-B5</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E5" s="130" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F5" s="129" t="str">
+        <x:f>IF(D5&gt;=E5,"Pass","Fail")</x:f>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="G5" s="129" t="str">
+        <x:v>1 − SLA breach rate; synthetic primary mechanics</x:v>
+      </x:c>
+      <x:c r="H5" s="129" t="str">
+        <x:v>Synthetic example; real target required</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="40" customHeight="1">
+      <x:c r="A6" s="103" t="str">
         <x:v>Repeat contacts per case</x:v>
       </x:c>
-      <x:c r="B5" s="132" t="n">
+      <x:c r="B6" s="105" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$I$2:$I$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="C5" s="132" t="n">
+      <x:c r="C6" s="105" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$I$2:$I$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
         <x:v>0.8333333333333334</x:v>
       </x:c>
-      <x:c r="D5" s="133" t="n">
-        <x:f>C5/B5-1</x:f>
+      <x:c r="D6" s="131" t="n">
+        <x:f>C6/B6-1</x:f>
         <x:v>-0.6666666666666666</x:v>
       </x:c>
-      <x:c r="E5" s="133" t="n">
+      <x:c r="E6" s="131" t="n">
         <x:v>-0.2</x:v>
       </x:c>
-      <x:c r="F5" s="131" t="str">
-        <x:f>IF(D5&lt;=E5,"Pass","Fail")</x:f>
+      <x:c r="F6" s="103" t="str">
+        <x:f>IF(D6&lt;=E6,"Pass","Fail")</x:f>
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="G5" s="131" t="str">
+      <x:c r="G6" s="103" t="str">
         <x:v>Average contact count per case</x:v>
       </x:c>
-      <x:c r="H5" s="131" t="str">
-        <x:v>Synthetic example</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="105" t="str">
+      <x:c r="H6" s="103" t="str">
+        <x:v>Synthetic secondary example</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="40" customHeight="1">
+      <x:c r="A7" s="103" t="str">
         <x:v>Confirmed-resolution time (hours)</x:v>
       </x:c>
-      <x:c r="B6" s="107" t="n">
+      <x:c r="B7" s="105" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$J$2:$J$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
         <x:v>47.833333333333336</x:v>
       </x:c>
-      <x:c r="C6" s="107" t="n">
+      <x:c r="C7" s="105" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$J$2:$J$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
         <x:v>26.666666666666668</x:v>
       </x:c>
-      <x:c r="D6" s="134" t="n">
-        <x:f>C6/B6-1</x:f>
+      <x:c r="D7" s="131" t="n">
+        <x:f>C7/B7-1</x:f>
         <x:v>-0.44250871080139376</x:v>
       </x:c>
-      <x:c r="E6" s="134" t="n">
+      <x:c r="E7" s="131" t="n">
         <x:v>-0.2</x:v>
       </x:c>
-      <x:c r="F6" s="105" t="str">
-        <x:f>IF(D6&lt;=E6,"Pass","Fail")</x:f>
+      <x:c r="F7" s="103" t="str">
+        <x:f>IF(D7&lt;=E7,"Pass","Fail")</x:f>
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="G6" s="105" t="str">
+      <x:c r="G7" s="103" t="str">
         <x:v>Average hours to confirmed outcome</x:v>
       </x:c>
-      <x:c r="H6" s="105" t="str">
-        <x:v>Synthetic example</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="40" customHeight="1">
-      <x:c r="A7" s="105" t="str">
+      <x:c r="H7" s="103" t="str">
+        <x:v>Synthetic secondary example</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="40" customHeight="1">
+      <x:c r="A8" s="103" t="str">
         <x:v>Understood next rate</x:v>
       </x:c>
-      <x:c r="B7" s="134" t="n">
+      <x:c r="B8" s="131" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$K$2:$K$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="134" t="n">
+      <x:c r="C8" s="131" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$K$2:$K$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="134" t="n">
-        <x:f>C7-B7</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="134" t="n">
+      <x:c r="D8" s="131" t="n">
+        <x:f>C8-B8</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="131" t="n">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="F7" s="105" t="str">
-        <x:f>IF(D7&gt;=E7,"Pass","Fail")</x:f>
+      <x:c r="F8" s="103" t="str">
+        <x:f>IF(D8&gt;=E8,"Pass","Fail")</x:f>
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="G7" s="105" t="str">
+      <x:c r="G8" s="103" t="str">
         <x:v>Share of cases with understood_next = 1</x:v>
       </x:c>
-      <x:c r="H7" s="105" t="str">
+      <x:c r="H8" s="103" t="str">
         <x:v>Synthetic proxy</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="40" customHeight="1">
-      <x:c r="A8" s="105" t="str">
+    <x:row r="9" ht="40" customHeight="1">
+      <x:c r="A9" s="103" t="str">
         <x:v>Incorrect recovery rate</x:v>
       </x:c>
-      <x:c r="B8" s="134" t="n">
+      <x:c r="B9" s="131" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$L$2:$L$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C8" s="134" t="n">
+      <x:c r="C9" s="131" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$L$2:$L$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D8" s="134" t="n">
-        <x:f>C8</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="134" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="105" t="str">
-        <x:f>IF(C8&lt;=E8,"Pass","Fail")</x:f>
+      <x:c r="D9" s="131" t="n">
+        <x:f>C9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="103" t="str">
+        <x:f>IF(C9&lt;=E9,"Pass","Fail")</x:f>
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="G8" s="105" t="str">
+      <x:c r="G9" s="103" t="str">
         <x:v>Share with incorrect_recovery = 1</x:v>
       </x:c>
-      <x:c r="H8" s="105" t="str">
+      <x:c r="H9" s="103" t="str">
         <x:v>Guardrail example</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
-      <x:c r="A9" s="105" t="str">
+    <x:row r="10" ht="40" customHeight="1">
+      <x:c r="A10" s="103" t="str">
         <x:v>SLA breach rate</x:v>
       </x:c>
-      <x:c r="B9" s="134" t="n">
+      <x:c r="B10" s="131" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$M$2:$M$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="C9" s="134" t="n">
+      <x:c r="C10" s="131" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$M$2:$M$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
         <x:v>0.16666666666666666</x:v>
       </x:c>
-      <x:c r="D9" s="134" t="n">
-        <x:f>C9</x:f>
+      <x:c r="D10" s="131" t="n">
+        <x:f>C10</x:f>
         <x:v>0.16666666666666666</x:v>
       </x:c>
-      <x:c r="E9" s="134" t="n">
+      <x:c r="E10" s="131" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="F9" s="105" t="str">
-        <x:f>IF(C9&lt;=E9,"Pass","Fail")</x:f>
+      <x:c r="F10" s="103" t="str">
+        <x:f>IF(C10&lt;=E10,"Pass","Fail")</x:f>
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="G9" s="105" t="str">
+      <x:c r="G10" s="103" t="str">
         <x:v>Share with sla_breach = 1</x:v>
       </x:c>
-      <x:c r="H9" s="105" t="str">
+      <x:c r="H10" s="103" t="str">
         <x:v>Guardrail example</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
-      <x:c r="A10" s="105" t="str">
+    <x:row r="11" ht="40" customHeight="1">
+      <x:c r="A11" s="103" t="str">
         <x:v>Support contacts per case</x:v>
       </x:c>
-      <x:c r="B10" s="107" t="n">
+      <x:c r="B11" s="105" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Baseline",'Case replay'!$N$2:$N$13)/COUNTIF('Case replay'!$B$2:$B$13,"Baseline")</x:f>
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="C10" s="107" t="n">
+      <x:c r="C11" s="105" t="n">
         <x:f>SUMIF('Case replay'!$B$2:$B$13,"Proposed",'Case replay'!$N$2:$N$13)/COUNTIF('Case replay'!$B$2:$B$13,"Proposed")</x:f>
         <x:v>0.8333333333333334</x:v>
       </x:c>
-      <x:c r="D10" s="134" t="n">
-        <x:f>C10/B10-1</x:f>
+      <x:c r="D11" s="131" t="n">
+        <x:f>C11/B11-1</x:f>
         <x:v>-0.6666666666666666</x:v>
       </x:c>
-      <x:c r="E10" s="134" t="n">
+      <x:c r="E11" s="131" t="n">
         <x:v>-0.2</x:v>
       </x:c>
-      <x:c r="F10" s="105" t="str">
-        <x:f>IF(D10&lt;=E10,"Pass","Fail")</x:f>
+      <x:c r="F11" s="103" t="str">
+        <x:f>IF(D11&lt;=E11,"Pass","Fail")</x:f>
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="G10" s="105" t="str">
+      <x:c r="G11" s="103" t="str">
         <x:v>Average support contact count per case</x:v>
       </x:c>
-      <x:c r="H10" s="105" t="str">
+      <x:c r="H11" s="103" t="str">
         <x:v>Synthetic example</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="109"/>
-      <x:c r="B11" s="109"/>
-      <x:c r="C11" s="109"/>
-      <x:c r="D11" s="109"/>
-      <x:c r="E11" s="109"/>
-      <x:c r="F11" s="109"/>
-      <x:c r="G11" s="109"/>
-      <x:c r="H11" s="109"/>
-    </x:row>
     <x:row r="12">
-      <x:c r="A12" s="135" t="str">
+      <x:c r="A12" s="132" t="str">
         <x:v>Overall recommendation</x:v>
       </x:c>
-      <x:c r="B12" s="135"/>
-      <x:c r="C12" s="135"/>
-      <x:c r="D12" s="135"/>
-      <x:c r="E12" s="135"/>
-      <x:c r="F12" s="135"/>
-      <x:c r="G12" s="135"/>
-      <x:c r="H12" s="135"/>
+      <x:c r="B12" s="132"/>
+      <x:c r="C12" s="132"/>
+      <x:c r="D12" s="132"/>
+      <x:c r="E12" s="132"/>
+      <x:c r="F12" s="132"/>
+      <x:c r="G12" s="132"/>
+      <x:c r="H12" s="132"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="136" t="str">
-        <x:f>IF(AND(F5="Pass",F6="Pass",F7="Pass",F8="Pass",F9="Pass",F10="Pass"),"Advance to controlled pilot preparation","Iterate before pilot")</x:f>
+      <x:c r="A13" s="133" t="str">
+        <x:f>IF(AND(F5="Pass",F6="Pass",F7="Pass",F8="Pass",F9="Pass",F10="Pass",F11="Pass"),"Advance to controlled pilot preparation","Iterate before pilot")</x:f>
         <x:v>Advance to controlled pilot preparation</x:v>
       </x:c>
-      <x:c r="B13" s="136"/>
-      <x:c r="C13" s="136"/>
-      <x:c r="D13" s="136"/>
-      <x:c r="E13" s="136"/>
-      <x:c r="F13" s="136"/>
-      <x:c r="G13" s="136"/>
-      <x:c r="H13" s="136"/>
+      <x:c r="B13" s="133"/>
+      <x:c r="C13" s="133"/>
+      <x:c r="D13" s="133"/>
+      <x:c r="E13" s="133"/>
+      <x:c r="F13" s="133"/>
+      <x:c r="G13" s="133"/>
+      <x:c r="H13" s="133"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1735,106 +1743,106 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="124" t="str">
         <x:v>Stage 5 Approval Log</x:v>
       </x:c>
-      <x:c r="B1" s="109"/>
-      <x:c r="C1" s="109"/>
-      <x:c r="D1" s="109"/>
-      <x:c r="E1" s="109"/>
+      <x:c r="B1" s="107"/>
+      <x:c r="C1" s="107"/>
+      <x:c r="D1" s="107"/>
+      <x:c r="E1" s="107"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="127" t="str">
+      <x:c r="A2" s="125" t="str">
         <x:v>Validation, measurement, pilot, and scale decisions</x:v>
       </x:c>
-      <x:c r="B2" s="109"/>
-      <x:c r="C2" s="109"/>
-      <x:c r="D2" s="109"/>
-      <x:c r="E2" s="109"/>
+      <x:c r="B2" s="107"/>
+      <x:c r="C2" s="107"/>
+      <x:c r="D2" s="107"/>
+      <x:c r="E2" s="107"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="109"/>
-      <x:c r="B3" s="109"/>
-      <x:c r="C3" s="109"/>
-      <x:c r="D3" s="109"/>
-      <x:c r="E3" s="109"/>
+      <x:c r="A3" s="107"/>
+      <x:c r="B3" s="107"/>
+      <x:c r="C3" s="107"/>
+      <x:c r="D3" s="107"/>
+      <x:c r="E3" s="107"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="128" t="str">
+      <x:c r="A4" s="126" t="str">
         <x:v>Decision ID</x:v>
       </x:c>
-      <x:c r="B4" s="129" t="str">
+      <x:c r="B4" s="127" t="str">
         <x:v>Decision</x:v>
       </x:c>
-      <x:c r="C4" s="129" t="str">
+      <x:c r="C4" s="127" t="str">
         <x:v>Recommendation</x:v>
       </x:c>
-      <x:c r="D4" s="129" t="str">
+      <x:c r="D4" s="127" t="str">
         <x:v>Reviewer decision</x:v>
       </x:c>
-      <x:c r="E4" s="130" t="str">
+      <x:c r="E4" s="128" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
-      <x:c r="A5" s="148" t="str">
+      <x:c r="A5" s="144" t="str">
         <x:v>V01</x:v>
       </x:c>
-      <x:c r="B5" s="148" t="str">
+      <x:c r="B5" s="144" t="str">
         <x:v>Validation protocol</x:v>
       </x:c>
-      <x:c r="C5" s="148" t="str">
+      <x:c r="C5" s="144" t="str">
         <x:v>Approve E1–E4 research and replay plan</x:v>
       </x:c>
-      <x:c r="D5" s="148" t="str">
+      <x:c r="D5" s="144" t="str">
         <x:v>Awaiting approval</x:v>
       </x:c>
-      <x:c r="E5" s="148" t="str"/>
+      <x:c r="E5" s="144" t="str"/>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
-      <x:c r="A6" s="149" t="str">
+      <x:c r="A6" s="145" t="str">
         <x:v>V02</x:v>
       </x:c>
-      <x:c r="B6" s="149" t="str">
+      <x:c r="B6" s="145" t="str">
         <x:v>Measurement contract</x:v>
       </x:c>
-      <x:c r="C6" s="149" t="str">
-        <x:v>Approve case-linked metrics and guardrails</x:v>
-      </x:c>
-      <x:c r="D6" s="149" t="str">
+      <x:c r="C6" s="145" t="str">
+        <x:v>Approve confirmed-resolution-within-SLA primary metric, case-linked cohort fields, and guardrails</x:v>
+      </x:c>
+      <x:c r="D6" s="145" t="str">
         <x:v>Awaiting approval</x:v>
       </x:c>
-      <x:c r="E6" s="149" t="str"/>
+      <x:c r="E6" s="145" t="str"/>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
-      <x:c r="A7" s="149" t="str">
+      <x:c r="A7" s="145" t="str">
         <x:v>V03</x:v>
       </x:c>
-      <x:c r="B7" s="149" t="str">
+      <x:c r="B7" s="145" t="str">
         <x:v>Controlled pilot</x:v>
       </x:c>
-      <x:c r="C7" s="149" t="str">
+      <x:c r="C7" s="145" t="str">
         <x:v>Proceed only after real baseline and readiness checks</x:v>
       </x:c>
-      <x:c r="D7" s="149" t="str">
+      <x:c r="D7" s="145" t="str">
         <x:v>Awaiting approval</x:v>
       </x:c>
-      <x:c r="E7" s="149" t="str"/>
+      <x:c r="E7" s="145" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
-      <x:c r="A8" s="149" t="str">
+      <x:c r="A8" s="145" t="str">
         <x:v>V04</x:v>
       </x:c>
-      <x:c r="B8" s="149" t="str">
+      <x:c r="B8" s="145" t="str">
         <x:v>Scale gate</x:v>
       </x:c>
-      <x:c r="C8" s="149" t="str">
+      <x:c r="C8" s="145" t="str">
         <x:v>Keep scale blocked until real pilot evidence passes</x:v>
       </x:c>
-      <x:c r="D8" s="149" t="str">
+      <x:c r="D8" s="145" t="str">
         <x:v>Blocked</x:v>
       </x:c>
-      <x:c r="E8" s="149" t="str"/>
+      <x:c r="E8" s="145" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
